--- a/excels/Sample.xlsx
+++ b/excels/Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\GameDataConfigTool\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C161CD4B-12EA-496D-8794-06931D4FC48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BE5FB8-EFC9-4681-8422-05CC4A63DEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8910" yWindow="6750" windowWidth="17130" windowHeight="13380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="53">
   <si>
     <t>战士</t>
   </si>
@@ -177,7 +177,13 @@
     <t>2025-07-14 00:00:19</t>
   </si>
   <si>
-    <t>Type|enum(SampleType)</t>
+    <t>Type|enum(SampleType)|nullable</t>
+  </si>
+  <si>
+    <t>未知生物</t>
+  </si>
+  <si>
+    <t>2000-01-01 00:00:00</t>
   </si>
 </sst>
 </file>
@@ -270,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -285,6 +291,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,11 +574,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.42578125" style="5" bestFit="1" customWidth="1"/>
@@ -1059,6 +1068,26 @@
         <v>49</v>
       </c>
     </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="6">
+        <v>999</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
